--- a/Data/LFJULIO.xlsx
+++ b/Data/LFJULIO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kespi\Downloads\lazarus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kespi\proyecto-datos.RC\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DEDCB93-1C0F-4626-8802-407BEEE4A61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F20C8C1-EFE7-4987-9753-4627018509E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7B2C86D8-C2E6-42D6-B4D7-0B84122BB8A2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{7B2C86D8-C2E6-42D6-B4D7-0B84122BB8A2}"/>
   </bookViews>
   <sheets>
     <sheet name="ENGATIVA" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="377">
   <si>
     <t>MOVIL</t>
   </si>
@@ -440,6 +440,738 @@
   </si>
   <si>
     <t>PLACA 2 RUTERO FRONTAL PERFORADA</t>
+  </si>
+  <si>
+    <t>Z10-4134</t>
+  </si>
+  <si>
+    <t>Z10-4159</t>
+  </si>
+  <si>
+    <t>Z10-4203</t>
+  </si>
+  <si>
+    <t>Z10-4209</t>
+  </si>
+  <si>
+    <t>Z10-4237</t>
+  </si>
+  <si>
+    <t>Z10-4253</t>
+  </si>
+  <si>
+    <t>Z10-4254</t>
+  </si>
+  <si>
+    <t>Z10-4263</t>
+  </si>
+  <si>
+    <t>Z10-4267</t>
+  </si>
+  <si>
+    <t>Z10-4269</t>
+  </si>
+  <si>
+    <t>Z10-4276</t>
+  </si>
+  <si>
+    <t>Z10-4274</t>
+  </si>
+  <si>
+    <t>Z10-4280</t>
+  </si>
+  <si>
+    <t>Z10-4286</t>
+  </si>
+  <si>
+    <t>Z10-4287</t>
+  </si>
+  <si>
+    <t>Z10-4293</t>
+  </si>
+  <si>
+    <t>Z10-4297</t>
+  </si>
+  <si>
+    <t>Z10-4304</t>
+  </si>
+  <si>
+    <t>Z10-4313</t>
+  </si>
+  <si>
+    <t>Z10-4315</t>
+  </si>
+  <si>
+    <t>Z10-4344</t>
+  </si>
+  <si>
+    <t>Z10-4348</t>
+  </si>
+  <si>
+    <t>Z10-4362</t>
+  </si>
+  <si>
+    <t>Z10-4366</t>
+  </si>
+  <si>
+    <t>Z10-4377</t>
+  </si>
+  <si>
+    <t>Z10-4386</t>
+  </si>
+  <si>
+    <t>Z10-4392</t>
+  </si>
+  <si>
+    <t>Z10-4399</t>
+  </si>
+  <si>
+    <t>Z10-4403</t>
+  </si>
+  <si>
+    <t>Z10-4405</t>
+  </si>
+  <si>
+    <t>Z10-4407</t>
+  </si>
+  <si>
+    <t>Z10-4423</t>
+  </si>
+  <si>
+    <t>Z10-4435</t>
+  </si>
+  <si>
+    <t>Z10-4439</t>
+  </si>
+  <si>
+    <t>Z10-4446</t>
+  </si>
+  <si>
+    <t>Z10-4457</t>
+  </si>
+  <si>
+    <t>Z10-4464</t>
+  </si>
+  <si>
+    <t>Z10-4467</t>
+  </si>
+  <si>
+    <t>Z10-4472</t>
+  </si>
+  <si>
+    <t>Z10-4480</t>
+  </si>
+  <si>
+    <t>Z10-4481</t>
+  </si>
+  <si>
+    <t>Z10-4496</t>
+  </si>
+  <si>
+    <t>Z10-4504</t>
+  </si>
+  <si>
+    <t>Z10-4513</t>
+  </si>
+  <si>
+    <t>Z10-4517</t>
+  </si>
+  <si>
+    <t>Z10-4536</t>
+  </si>
+  <si>
+    <t>Z10-4540</t>
+  </si>
+  <si>
+    <t>Z10-4548</t>
+  </si>
+  <si>
+    <t>Z10-4554</t>
+  </si>
+  <si>
+    <t>Z10-4558</t>
+  </si>
+  <si>
+    <t>Z10-4562</t>
+  </si>
+  <si>
+    <t>Z10-4566</t>
+  </si>
+  <si>
+    <t>Z10-4597</t>
+  </si>
+  <si>
+    <t>Z10-4604</t>
+  </si>
+  <si>
+    <t>Z10-4609</t>
+  </si>
+  <si>
+    <t>Z10-4618</t>
+  </si>
+  <si>
+    <t>Z10-4619</t>
+  </si>
+  <si>
+    <t>Z10-4639</t>
+  </si>
+  <si>
+    <t>Z10-4641</t>
+  </si>
+  <si>
+    <t>Z10-4642</t>
+  </si>
+  <si>
+    <t>Z10-4690</t>
+  </si>
+  <si>
+    <t>Z10-7125</t>
+  </si>
+  <si>
+    <t>Z10-7126</t>
+  </si>
+  <si>
+    <t>Z10-7127</t>
+  </si>
+  <si>
+    <t>Z10-7128</t>
+  </si>
+  <si>
+    <t>Z10-7129</t>
+  </si>
+  <si>
+    <t>Z10-7132</t>
+  </si>
+  <si>
+    <t>Z10-7133</t>
+  </si>
+  <si>
+    <t>Z10-7134</t>
+  </si>
+  <si>
+    <t>Z10-7135</t>
+  </si>
+  <si>
+    <t>Z10-7137</t>
+  </si>
+  <si>
+    <t>Z10-7138</t>
+  </si>
+  <si>
+    <t>Z10-7139</t>
+  </si>
+  <si>
+    <t>Z10-7140</t>
+  </si>
+  <si>
+    <t>Z10-7142</t>
+  </si>
+  <si>
+    <t>Z10-7143</t>
+  </si>
+  <si>
+    <t>Z10-7144</t>
+  </si>
+  <si>
+    <t>Z10-7145</t>
+  </si>
+  <si>
+    <t>Z10-7146</t>
+  </si>
+  <si>
+    <t>Z10-7147</t>
+  </si>
+  <si>
+    <t>Z10-7148</t>
+  </si>
+  <si>
+    <t>Z10-7149</t>
+  </si>
+  <si>
+    <t>Z10-7151</t>
+  </si>
+  <si>
+    <t>Z10-7152</t>
+  </si>
+  <si>
+    <t>Z10-7153</t>
+  </si>
+  <si>
+    <t>Z10-7154</t>
+  </si>
+  <si>
+    <t>Z10-7155</t>
+  </si>
+  <si>
+    <t>Z10-7156</t>
+  </si>
+  <si>
+    <t>Z10-7157</t>
+  </si>
+  <si>
+    <t>Z10-7159</t>
+  </si>
+  <si>
+    <t>Z10-7160</t>
+  </si>
+  <si>
+    <t>Z10-7161</t>
+  </si>
+  <si>
+    <t>Z10-7162</t>
+  </si>
+  <si>
+    <t>Z10-7163</t>
+  </si>
+  <si>
+    <t>Z10-7164</t>
+  </si>
+  <si>
+    <t>Z10-7165</t>
+  </si>
+  <si>
+    <t>Z10-7166</t>
+  </si>
+  <si>
+    <t>Z10-7168</t>
+  </si>
+  <si>
+    <t>Z10-7169</t>
+  </si>
+  <si>
+    <t>Z10-7170</t>
+  </si>
+  <si>
+    <t>Z10-7171</t>
+  </si>
+  <si>
+    <t>Z10-7172</t>
+  </si>
+  <si>
+    <t>Z10-7178</t>
+  </si>
+  <si>
+    <t>Z10-7187</t>
+  </si>
+  <si>
+    <t>Z10-7203</t>
+  </si>
+  <si>
+    <t>Z10-7251</t>
+  </si>
+  <si>
+    <t>Z10-7252</t>
+  </si>
+  <si>
+    <t>Z10-7253</t>
+  </si>
+  <si>
+    <t>Z10-7254</t>
+  </si>
+  <si>
+    <t>Z10-7255</t>
+  </si>
+  <si>
+    <t>Z10-7256</t>
+  </si>
+  <si>
+    <t>Z10-7257</t>
+  </si>
+  <si>
+    <t>Z10-7260</t>
+  </si>
+  <si>
+    <t>Z10-7291</t>
+  </si>
+  <si>
+    <t>Z10-7292</t>
+  </si>
+  <si>
+    <t>Z10-7295</t>
+  </si>
+  <si>
+    <t>Z10-7296</t>
+  </si>
+  <si>
+    <t>Z10-7300</t>
+  </si>
+  <si>
+    <t>Z10-7301</t>
+  </si>
+  <si>
+    <t>Z10-7331</t>
+  </si>
+  <si>
+    <t>Z10-4440</t>
+  </si>
+  <si>
+    <t>Z10-4575</t>
+  </si>
+  <si>
+    <t>Z10-4683</t>
+  </si>
+  <si>
+    <t>Z10-2131</t>
+  </si>
+  <si>
+    <t>Z10-2133</t>
+  </si>
+  <si>
+    <t>Z10-2144</t>
+  </si>
+  <si>
+    <t>Z10-2151</t>
+  </si>
+  <si>
+    <t>Z10-2152</t>
+  </si>
+  <si>
+    <t>Z10-2154</t>
+  </si>
+  <si>
+    <t>Z10-2155</t>
+  </si>
+  <si>
+    <t>Z10-2161</t>
+  </si>
+  <si>
+    <t>Z10-2164</t>
+  </si>
+  <si>
+    <t>Z10-2179</t>
+  </si>
+  <si>
+    <t>Z10-2180</t>
+  </si>
+  <si>
+    <t>Z10-2181</t>
+  </si>
+  <si>
+    <t>Z10-2183</t>
+  </si>
+  <si>
+    <t>Z10-2185</t>
+  </si>
+  <si>
+    <t>Z10-2186</t>
+  </si>
+  <si>
+    <t>Z10-2193</t>
+  </si>
+  <si>
+    <t>Z10-2201</t>
+  </si>
+  <si>
+    <t>Z10-2227</t>
+  </si>
+  <si>
+    <t>Z10-2245</t>
+  </si>
+  <si>
+    <t>Z10-2263</t>
+  </si>
+  <si>
+    <t>Z10-2271</t>
+  </si>
+  <si>
+    <t>Z10-2275</t>
+  </si>
+  <si>
+    <t>Z10-4270</t>
+  </si>
+  <si>
+    <t>Z10-4278</t>
+  </si>
+  <si>
+    <t>Z10-4284</t>
+  </si>
+  <si>
+    <t>Z10-4279</t>
+  </si>
+  <si>
+    <t>Z10-4288</t>
+  </si>
+  <si>
+    <t>Z10-4289</t>
+  </si>
+  <si>
+    <t>Z10-4299</t>
+  </si>
+  <si>
+    <t>Z10-4301</t>
+  </si>
+  <si>
+    <t>Z10-4306</t>
+  </si>
+  <si>
+    <t>Z10-4312</t>
+  </si>
+  <si>
+    <t>Z10-4316</t>
+  </si>
+  <si>
+    <t>Z10-4321</t>
+  </si>
+  <si>
+    <t>Z10-4325</t>
+  </si>
+  <si>
+    <t>Z10-4333</t>
+  </si>
+  <si>
+    <t>Z10-4338</t>
+  </si>
+  <si>
+    <t>Z10-4342</t>
+  </si>
+  <si>
+    <t>Z10-4343</t>
+  </si>
+  <si>
+    <t>Z10-4345</t>
+  </si>
+  <si>
+    <t>Z10-4353</t>
+  </si>
+  <si>
+    <t>Z10-4370</t>
+  </si>
+  <si>
+    <t>Z10-4371</t>
+  </si>
+  <si>
+    <t>Z10-4373</t>
+  </si>
+  <si>
+    <t>Z10-4376</t>
+  </si>
+  <si>
+    <t>Z10-4378</t>
+  </si>
+  <si>
+    <t>Z10-4381</t>
+  </si>
+  <si>
+    <t>Z10-4382</t>
+  </si>
+  <si>
+    <t>Z10-4388</t>
+  </si>
+  <si>
+    <t>Z10-4389</t>
+  </si>
+  <si>
+    <t>Z10-4391</t>
+  </si>
+  <si>
+    <t>Z10-4406</t>
+  </si>
+  <si>
+    <t>Z10-4409</t>
+  </si>
+  <si>
+    <t>Z10-4412</t>
+  </si>
+  <si>
+    <t>Z10-4418</t>
+  </si>
+  <si>
+    <t>Z10-4425</t>
+  </si>
+  <si>
+    <t>Z10-4426</t>
+  </si>
+  <si>
+    <t>Z10-4427</t>
+  </si>
+  <si>
+    <t>Z10-4431</t>
+  </si>
+  <si>
+    <t>Z10-4436</t>
+  </si>
+  <si>
+    <t>Z10-4441</t>
+  </si>
+  <si>
+    <t>Z10-4447</t>
+  </si>
+  <si>
+    <t>Z10-4449</t>
+  </si>
+  <si>
+    <t>Z10-4450</t>
+  </si>
+  <si>
+    <t>Z10-4451</t>
+  </si>
+  <si>
+    <t>Z10-4454</t>
+  </si>
+  <si>
+    <t>Z10-4458</t>
+  </si>
+  <si>
+    <t>Z10-4484</t>
+  </si>
+  <si>
+    <t>Z10-4486</t>
+  </si>
+  <si>
+    <t>Z10-4497</t>
+  </si>
+  <si>
+    <t>Z10-4498</t>
+  </si>
+  <si>
+    <t>Z10-4499</t>
+  </si>
+  <si>
+    <t>Z10-4503</t>
+  </si>
+  <si>
+    <t>Z10-4507</t>
+  </si>
+  <si>
+    <t>Z10-4508</t>
+  </si>
+  <si>
+    <t>Z10-4511</t>
+  </si>
+  <si>
+    <t>Z10-4521</t>
+  </si>
+  <si>
+    <t>Z10-4523</t>
+  </si>
+  <si>
+    <t>Z10-4530</t>
+  </si>
+  <si>
+    <t>Z10-4541</t>
+  </si>
+  <si>
+    <t>Z10-4543</t>
+  </si>
+  <si>
+    <t>Z10-4549</t>
+  </si>
+  <si>
+    <t>Z10-4550</t>
+  </si>
+  <si>
+    <t>Z10-4565</t>
+  </si>
+  <si>
+    <t>Z10-4567</t>
+  </si>
+  <si>
+    <t>Z10-4568</t>
+  </si>
+  <si>
+    <t>Z10-4573</t>
+  </si>
+  <si>
+    <t>Z10-4579</t>
+  </si>
+  <si>
+    <t>Z10-4583</t>
+  </si>
+  <si>
+    <t>Z10-4587</t>
+  </si>
+  <si>
+    <t>Z10-4592</t>
+  </si>
+  <si>
+    <t>Z10-4593</t>
+  </si>
+  <si>
+    <t>Z10-4594</t>
+  </si>
+  <si>
+    <t>Z10-4598</t>
+  </si>
+  <si>
+    <t>Z10-4599</t>
+  </si>
+  <si>
+    <t>Z10-4600</t>
+  </si>
+  <si>
+    <t>Z10-4606</t>
+  </si>
+  <si>
+    <t>Z10-4605</t>
+  </si>
+  <si>
+    <t>Z10-4608</t>
+  </si>
+  <si>
+    <t>Z10-4613</t>
+  </si>
+  <si>
+    <t>Z10-4620</t>
+  </si>
+  <si>
+    <t>Z10-4627</t>
+  </si>
+  <si>
+    <t>Z10-4632</t>
+  </si>
+  <si>
+    <t>Z10-4638</t>
+  </si>
+  <si>
+    <t>Z10-4684</t>
+  </si>
+  <si>
+    <t>Z10-7267</t>
+  </si>
+  <si>
+    <t>Z10-7282</t>
+  </si>
+  <si>
+    <t>Z10-7283</t>
+  </si>
+  <si>
+    <t>Z10-7294</t>
+  </si>
+  <si>
+    <t>Z10-7323</t>
+  </si>
+  <si>
+    <t>Z10-7324</t>
+  </si>
+  <si>
+    <t>Z10-7326</t>
+  </si>
+  <si>
+    <t>Z10-7327</t>
+  </si>
+  <si>
+    <t>Z10-7328</t>
+  </si>
+  <si>
+    <t>Z10-7332</t>
+  </si>
+  <si>
+    <t>Z10-7333</t>
+  </si>
+  <si>
+    <t>Z10-4275</t>
+  </si>
+  <si>
+    <t>Z10-4384</t>
+  </si>
+  <si>
+    <t>Z10-4445</t>
+  </si>
+  <si>
+    <t>Z10-4559</t>
+  </si>
+  <si>
+    <t>Z10-4648</t>
   </si>
 </sst>
 </file>
@@ -3470,7 +4202,7 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
@@ -3505,10 +4237,10 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="6"/>
-      <c r="B2" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="A2" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B2" s="3"/>
       <c r="C2" s="3" t="b">
         <v>0</v>
       </c>
@@ -3524,7 +4256,9 @@
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="6"/>
+      <c r="A3" s="6" t="s">
+        <v>257</v>
+      </c>
       <c r="B3" s="3" t="b">
         <v>0</v>
       </c>
@@ -3543,7 +4277,9 @@
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="6"/>
+      <c r="A4" s="6" t="s">
+        <v>258</v>
+      </c>
       <c r="B4" s="3" t="b">
         <v>0</v>
       </c>
@@ -3562,7 +4298,9 @@
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
+      <c r="A5" s="6" t="s">
+        <v>259</v>
+      </c>
       <c r="B5" s="3" t="b">
         <v>0</v>
       </c>
@@ -3581,7 +4319,9 @@
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="6"/>
+      <c r="A6" s="6" t="s">
+        <v>260</v>
+      </c>
       <c r="B6" s="3" t="b">
         <v>0</v>
       </c>
@@ -3600,7 +4340,9 @@
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="6"/>
+      <c r="A7" s="6" t="s">
+        <v>261</v>
+      </c>
       <c r="B7" s="3" t="b">
         <v>0</v>
       </c>
@@ -3619,7 +4361,9 @@
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="6"/>
+      <c r="A8" s="6" t="s">
+        <v>262</v>
+      </c>
       <c r="B8" s="3" t="b">
         <v>0</v>
       </c>
@@ -3638,7 +4382,9 @@
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="6"/>
+      <c r="A9" s="6" t="s">
+        <v>263</v>
+      </c>
       <c r="B9" s="3" t="b">
         <v>0</v>
       </c>
@@ -3657,7 +4403,9 @@
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="6"/>
+      <c r="A10" s="6" t="s">
+        <v>264</v>
+      </c>
       <c r="B10" s="3" t="b">
         <v>0</v>
       </c>
@@ -3676,7 +4424,9 @@
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="6"/>
+      <c r="A11" s="6" t="s">
+        <v>265</v>
+      </c>
       <c r="B11" s="3" t="b">
         <v>0</v>
       </c>
@@ -3695,7 +4445,9 @@
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="6"/>
+      <c r="A12" s="6" t="s">
+        <v>266</v>
+      </c>
       <c r="B12" s="3" t="b">
         <v>0</v>
       </c>
@@ -3714,7 +4466,9 @@
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="6"/>
+      <c r="A13" s="6" t="s">
+        <v>267</v>
+      </c>
       <c r="B13" s="3" t="b">
         <v>0</v>
       </c>
@@ -3733,7 +4487,9 @@
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="6"/>
+      <c r="A14" s="6" t="s">
+        <v>268</v>
+      </c>
       <c r="B14" s="3" t="b">
         <v>0</v>
       </c>
@@ -3752,7 +4508,9 @@
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="6"/>
+      <c r="A15" s="6" t="s">
+        <v>269</v>
+      </c>
       <c r="B15" s="3" t="b">
         <v>0</v>
       </c>
@@ -3771,7 +4529,9 @@
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="6"/>
+      <c r="A16" s="6" t="s">
+        <v>270</v>
+      </c>
       <c r="B16" s="3" t="b">
         <v>0</v>
       </c>
@@ -3790,7 +4550,9 @@
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="6"/>
+      <c r="A17" s="6" t="s">
+        <v>271</v>
+      </c>
       <c r="B17" s="3" t="b">
         <v>0</v>
       </c>
@@ -3809,7 +4571,9 @@
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="6"/>
+      <c r="A18" s="6" t="s">
+        <v>272</v>
+      </c>
       <c r="B18" s="3" t="b">
         <v>0</v>
       </c>
@@ -3828,7 +4592,9 @@
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="6"/>
+      <c r="A19" s="6" t="s">
+        <v>273</v>
+      </c>
       <c r="B19" s="3" t="b">
         <v>0</v>
       </c>
@@ -3847,7 +4613,9 @@
       <c r="G19" s="2"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="6"/>
+      <c r="A20" s="6" t="s">
+        <v>274</v>
+      </c>
       <c r="B20" s="3" t="b">
         <v>0</v>
       </c>
@@ -3866,7 +4634,9 @@
       <c r="G20" s="2"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="6"/>
+      <c r="A21" s="6" t="s">
+        <v>275</v>
+      </c>
       <c r="B21" s="3" t="b">
         <v>0</v>
       </c>
@@ -3885,7 +4655,9 @@
       <c r="G21" s="2"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="6"/>
+      <c r="A22" s="6" t="s">
+        <v>276</v>
+      </c>
       <c r="B22" s="3" t="b">
         <v>0</v>
       </c>
@@ -3904,7 +4676,9 @@
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="6"/>
+      <c r="A23" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="B23" s="3" t="b">
         <v>0</v>
       </c>
@@ -3923,7 +4697,9 @@
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="6"/>
+      <c r="A24" s="6" t="s">
+        <v>278</v>
+      </c>
       <c r="B24" s="3" t="b">
         <v>0</v>
       </c>
@@ -3942,7 +4718,9 @@
       <c r="G24" s="2"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="6"/>
+      <c r="A25" s="6" t="s">
+        <v>279</v>
+      </c>
       <c r="B25" s="3" t="b">
         <v>0</v>
       </c>
@@ -3961,7 +4739,9 @@
       <c r="G25" s="2"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="6"/>
+      <c r="A26" s="6" t="s">
+        <v>281</v>
+      </c>
       <c r="B26" s="3" t="b">
         <v>0</v>
       </c>
@@ -3980,7 +4760,9 @@
       <c r="G26" s="2"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="6"/>
+      <c r="A27" s="6" t="s">
+        <v>280</v>
+      </c>
       <c r="B27" s="3" t="b">
         <v>0</v>
       </c>
@@ -3999,7 +4781,9 @@
       <c r="G27" s="2"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" s="6"/>
+      <c r="A28" s="6" t="s">
+        <v>282</v>
+      </c>
       <c r="B28" s="3" t="b">
         <v>0</v>
       </c>
@@ -4018,7 +4802,9 @@
       <c r="G28" s="2"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="6"/>
+      <c r="A29" s="6" t="s">
+        <v>283</v>
+      </c>
       <c r="B29" s="3" t="b">
         <v>0</v>
       </c>
@@ -4037,7 +4823,9 @@
       <c r="G29" s="2"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="6"/>
+      <c r="A30" s="6" t="s">
+        <v>284</v>
+      </c>
       <c r="B30" s="3" t="b">
         <v>0</v>
       </c>
@@ -4056,7 +4844,9 @@
       <c r="G30" s="2"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="6"/>
+      <c r="A31" s="6" t="s">
+        <v>285</v>
+      </c>
       <c r="B31" s="3" t="b">
         <v>0</v>
       </c>
@@ -4075,7 +4865,9 @@
       <c r="G31" s="2"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="6"/>
+      <c r="A32" s="6" t="s">
+        <v>286</v>
+      </c>
       <c r="B32" s="3" t="b">
         <v>0</v>
       </c>
@@ -4094,7 +4886,9 @@
       <c r="G32" s="2"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="6"/>
+      <c r="A33" s="6" t="s">
+        <v>287</v>
+      </c>
       <c r="B33" s="3" t="b">
         <v>0</v>
       </c>
@@ -4113,7 +4907,9 @@
       <c r="G33" s="2"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="6"/>
+      <c r="A34" s="6" t="s">
+        <v>288</v>
+      </c>
       <c r="B34" s="3" t="b">
         <v>0</v>
       </c>
@@ -4132,7 +4928,9 @@
       <c r="G34" s="2"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="6"/>
+      <c r="A35" s="6" t="s">
+        <v>289</v>
+      </c>
       <c r="B35" s="3" t="b">
         <v>0</v>
       </c>
@@ -4151,7 +4949,9 @@
       <c r="G35" s="2"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="6"/>
+      <c r="A36" s="6" t="s">
+        <v>290</v>
+      </c>
       <c r="B36" s="3" t="b">
         <v>0</v>
       </c>
@@ -4170,7 +4970,9 @@
       <c r="G36" s="2"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="6"/>
+      <c r="A37" s="6" t="s">
+        <v>291</v>
+      </c>
       <c r="B37" s="3" t="b">
         <v>0</v>
       </c>
@@ -4189,7 +4991,9 @@
       <c r="G37" s="2"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="6"/>
+      <c r="A38" s="6" t="s">
+        <v>292</v>
+      </c>
       <c r="B38" s="3" t="b">
         <v>0</v>
       </c>
@@ -4208,7 +5012,9 @@
       <c r="G38" s="2"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" s="6"/>
+      <c r="A39" s="6" t="s">
+        <v>293</v>
+      </c>
       <c r="B39" s="3" t="b">
         <v>0</v>
       </c>
@@ -4227,7 +5033,9 @@
       <c r="G39" s="2"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="6"/>
+      <c r="A40" s="6" t="s">
+        <v>294</v>
+      </c>
       <c r="B40" s="3" t="b">
         <v>0</v>
       </c>
@@ -4246,7 +5054,9 @@
       <c r="G40" s="2"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="6"/>
+      <c r="A41" s="6" t="s">
+        <v>295</v>
+      </c>
       <c r="B41" s="3" t="b">
         <v>0</v>
       </c>
@@ -4265,7 +5075,9 @@
       <c r="G41" s="2"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" s="6"/>
+      <c r="A42" s="6" t="s">
+        <v>296</v>
+      </c>
       <c r="B42" s="3" t="b">
         <v>0</v>
       </c>
@@ -4284,7 +5096,9 @@
       <c r="G42" s="2"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="6"/>
+      <c r="A43" s="6" t="s">
+        <v>297</v>
+      </c>
       <c r="B43" s="3" t="b">
         <v>0</v>
       </c>
@@ -4303,7 +5117,9 @@
       <c r="G43" s="2"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="6"/>
+      <c r="A44" s="6" t="s">
+        <v>298</v>
+      </c>
       <c r="B44" s="3" t="b">
         <v>0</v>
       </c>
@@ -4322,7 +5138,9 @@
       <c r="G44" s="2"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="6"/>
+      <c r="A45" s="6" t="s">
+        <v>299</v>
+      </c>
       <c r="B45" s="3" t="b">
         <v>0</v>
       </c>
@@ -4341,7 +5159,9 @@
       <c r="G45" s="2"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" s="6"/>
+      <c r="A46" s="6" t="s">
+        <v>300</v>
+      </c>
       <c r="B46" s="3" t="b">
         <v>0</v>
       </c>
@@ -4360,7 +5180,9 @@
       <c r="G46" s="2"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="6"/>
+      <c r="A47" s="6" t="s">
+        <v>301</v>
+      </c>
       <c r="B47" s="3" t="b">
         <v>0</v>
       </c>
@@ -4379,7 +5201,9 @@
       <c r="G47" s="2"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" s="6"/>
+      <c r="A48" s="6" t="s">
+        <v>302</v>
+      </c>
       <c r="B48" s="3" t="b">
         <v>0</v>
       </c>
@@ -4398,7 +5222,9 @@
       <c r="G48" s="2"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A49" s="6"/>
+      <c r="A49" s="6" t="s">
+        <v>303</v>
+      </c>
       <c r="B49" s="3" t="b">
         <v>0</v>
       </c>
@@ -4417,7 +5243,9 @@
       <c r="G49" s="2"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A50" s="6"/>
+      <c r="A50" s="6" t="s">
+        <v>304</v>
+      </c>
       <c r="B50" s="3" t="b">
         <v>0</v>
       </c>
@@ -4436,7 +5264,9 @@
       <c r="G50" s="2"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A51" s="6"/>
+      <c r="A51" s="6" t="s">
+        <v>305</v>
+      </c>
       <c r="B51" s="3" t="b">
         <v>0</v>
       </c>
@@ -4455,7 +5285,9 @@
       <c r="G51" s="2"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52" s="6"/>
+      <c r="A52" s="6" t="s">
+        <v>306</v>
+      </c>
       <c r="B52" s="3" t="b">
         <v>0</v>
       </c>
@@ -4474,7 +5306,9 @@
       <c r="G52" s="2"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53" s="6"/>
+      <c r="A53" s="6" t="s">
+        <v>307</v>
+      </c>
       <c r="B53" s="3" t="b">
         <v>0</v>
       </c>
@@ -4493,7 +5327,9 @@
       <c r="G53" s="2"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" s="6"/>
+      <c r="A54" s="6" t="s">
+        <v>308</v>
+      </c>
       <c r="B54" s="3" t="b">
         <v>0</v>
       </c>
@@ -4512,7 +5348,9 @@
       <c r="G54" s="2"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A55" s="6"/>
+      <c r="A55" s="6" t="s">
+        <v>309</v>
+      </c>
       <c r="B55" s="3" t="b">
         <v>0</v>
       </c>
@@ -4531,7 +5369,9 @@
       <c r="G55" s="2"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56" s="6"/>
+      <c r="A56" s="6" t="s">
+        <v>310</v>
+      </c>
       <c r="B56" s="3" t="b">
         <v>0</v>
       </c>
@@ -4550,7 +5390,9 @@
       <c r="G56" s="2"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A57" s="6"/>
+      <c r="A57" s="6" t="s">
+        <v>311</v>
+      </c>
       <c r="B57" s="3" t="b">
         <v>0</v>
       </c>
@@ -4569,7 +5411,9 @@
       <c r="G57" s="2"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A58" s="6"/>
+      <c r="A58" s="6" t="s">
+        <v>312</v>
+      </c>
       <c r="B58" s="3" t="b">
         <v>0</v>
       </c>
@@ -4588,7 +5432,9 @@
       <c r="G58" s="2"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A59" s="6"/>
+      <c r="A59" s="6" t="s">
+        <v>313</v>
+      </c>
       <c r="B59" s="3" t="b">
         <v>0</v>
       </c>
@@ -4607,7 +5453,9 @@
       <c r="G59" s="2"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A60" s="6"/>
+      <c r="A60" s="6" t="s">
+        <v>314</v>
+      </c>
       <c r="B60" s="3" t="b">
         <v>0</v>
       </c>
@@ -4626,7 +5474,9 @@
       <c r="G60" s="2"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A61" s="6"/>
+      <c r="A61" s="6" t="s">
+        <v>315</v>
+      </c>
       <c r="B61" s="3" t="b">
         <v>0</v>
       </c>
@@ -4645,7 +5495,9 @@
       <c r="G61" s="2"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A62" s="6"/>
+      <c r="A62" s="6" t="s">
+        <v>316</v>
+      </c>
       <c r="B62" s="3" t="b">
         <v>0</v>
       </c>
@@ -4664,7 +5516,9 @@
       <c r="G62" s="2"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A63" s="6"/>
+      <c r="A63" s="6" t="s">
+        <v>317</v>
+      </c>
       <c r="B63" s="3" t="b">
         <v>0</v>
       </c>
@@ -4683,7 +5537,9 @@
       <c r="G63" s="2"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A64" s="6"/>
+      <c r="A64" s="6" t="s">
+        <v>318</v>
+      </c>
       <c r="B64" s="3" t="b">
         <v>0</v>
       </c>
@@ -4702,7 +5558,9 @@
       <c r="G64" s="2"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A65" s="6"/>
+      <c r="A65" s="6" t="s">
+        <v>319</v>
+      </c>
       <c r="B65" s="3" t="b">
         <v>0</v>
       </c>
@@ -4721,7 +5579,9 @@
       <c r="G65" s="2"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A66" s="6"/>
+      <c r="A66" s="6" t="s">
+        <v>320</v>
+      </c>
       <c r="B66" s="3" t="b">
         <v>0</v>
       </c>
@@ -4740,7 +5600,9 @@
       <c r="G66" s="2"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A67" s="6"/>
+      <c r="A67" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="B67" s="3" t="b">
         <v>0</v>
       </c>
@@ -4759,7 +5621,9 @@
       <c r="G67" s="2"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A68" s="6"/>
+      <c r="A68" s="6" t="s">
+        <v>322</v>
+      </c>
       <c r="B68" s="3" t="b">
         <v>0</v>
       </c>
@@ -4778,7 +5642,9 @@
       <c r="G68" s="2"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A69" s="6"/>
+      <c r="A69" s="6" t="s">
+        <v>323</v>
+      </c>
       <c r="B69" s="3" t="b">
         <v>0</v>
       </c>
@@ -4797,7 +5663,9 @@
       <c r="G69" s="2"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A70" s="6"/>
+      <c r="A70" s="6" t="s">
+        <v>324</v>
+      </c>
       <c r="B70" s="3" t="b">
         <v>0</v>
       </c>
@@ -4816,7 +5684,9 @@
       <c r="G70" s="2"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A71" s="6"/>
+      <c r="A71" s="6" t="s">
+        <v>325</v>
+      </c>
       <c r="B71" s="3" t="b">
         <v>0</v>
       </c>
@@ -4835,7 +5705,9 @@
       <c r="G71" s="2"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A72" s="6"/>
+      <c r="A72" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="B72" s="3" t="b">
         <v>0</v>
       </c>
@@ -4854,7 +5726,9 @@
       <c r="G72" s="2"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A73" s="6"/>
+      <c r="A73" s="6" t="s">
+        <v>327</v>
+      </c>
       <c r="B73" s="3" t="b">
         <v>0</v>
       </c>
@@ -4873,7 +5747,9 @@
       <c r="G73" s="2"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A74" s="6"/>
+      <c r="A74" s="6" t="s">
+        <v>328</v>
+      </c>
       <c r="B74" s="3" t="b">
         <v>0</v>
       </c>
@@ -4892,7 +5768,9 @@
       <c r="G74" s="2"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A75" s="6"/>
+      <c r="A75" s="6" t="s">
+        <v>329</v>
+      </c>
       <c r="B75" s="3" t="b">
         <v>0</v>
       </c>
@@ -4911,7 +5789,9 @@
       <c r="G75" s="2"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A76" s="6"/>
+      <c r="A76" s="6" t="s">
+        <v>330</v>
+      </c>
       <c r="B76" s="3" t="b">
         <v>0</v>
       </c>
@@ -4930,7 +5810,9 @@
       <c r="G76" s="2"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A77" s="6"/>
+      <c r="A77" s="6" t="s">
+        <v>331</v>
+      </c>
       <c r="B77" s="3" t="b">
         <v>0</v>
       </c>
@@ -4949,7 +5831,9 @@
       <c r="G77" s="2"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A78" s="6"/>
+      <c r="A78" s="6" t="s">
+        <v>332</v>
+      </c>
       <c r="B78" s="3" t="b">
         <v>0</v>
       </c>
@@ -4968,7 +5852,9 @@
       <c r="G78" s="2"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A79" s="6"/>
+      <c r="A79" s="6" t="s">
+        <v>333</v>
+      </c>
       <c r="B79" s="3" t="b">
         <v>0</v>
       </c>
@@ -4987,7 +5873,9 @@
       <c r="G79" s="2"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A80" s="6"/>
+      <c r="A80" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="B80" s="3" t="b">
         <v>0</v>
       </c>
@@ -5006,7 +5894,9 @@
       <c r="G80" s="2"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A81" s="6"/>
+      <c r="A81" s="6" t="s">
+        <v>335</v>
+      </c>
       <c r="B81" s="3" t="b">
         <v>0</v>
       </c>
@@ -5025,7 +5915,9 @@
       <c r="G81" s="2"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A82" s="6"/>
+      <c r="A82" s="6" t="s">
+        <v>336</v>
+      </c>
       <c r="B82" s="3" t="b">
         <v>0</v>
       </c>
@@ -5044,7 +5936,9 @@
       <c r="G82" s="2"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A83" s="6"/>
+      <c r="A83" s="6" t="s">
+        <v>337</v>
+      </c>
       <c r="B83" s="3" t="b">
         <v>0</v>
       </c>
@@ -5063,7 +5957,9 @@
       <c r="G83" s="2"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A84" s="6"/>
+      <c r="A84" s="6" t="s">
+        <v>338</v>
+      </c>
       <c r="B84" s="3" t="b">
         <v>0</v>
       </c>
@@ -5082,7 +5978,9 @@
       <c r="G84" s="2"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A85" s="6"/>
+      <c r="A85" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="B85" s="3" t="b">
         <v>0</v>
       </c>
@@ -5101,7 +5999,9 @@
       <c r="G85" s="2"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A86" s="6"/>
+      <c r="A86" s="6" t="s">
+        <v>340</v>
+      </c>
       <c r="B86" s="3" t="b">
         <v>0</v>
       </c>
@@ -5120,7 +6020,9 @@
       <c r="G86" s="2"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A87" s="6"/>
+      <c r="A87" s="6" t="s">
+        <v>341</v>
+      </c>
       <c r="B87" s="3" t="b">
         <v>0</v>
       </c>
@@ -5139,7 +6041,9 @@
       <c r="G87" s="2"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A88" s="6"/>
+      <c r="A88" s="6" t="s">
+        <v>342</v>
+      </c>
       <c r="B88" s="3" t="b">
         <v>0</v>
       </c>
@@ -5158,7 +6062,9 @@
       <c r="G88" s="2"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A89" s="6"/>
+      <c r="A89" s="6" t="s">
+        <v>343</v>
+      </c>
       <c r="B89" s="3" t="b">
         <v>0</v>
       </c>
@@ -5177,7 +6083,9 @@
       <c r="G89" s="2"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A90" s="6"/>
+      <c r="A90" s="6" t="s">
+        <v>344</v>
+      </c>
       <c r="B90" s="3" t="b">
         <v>0</v>
       </c>
@@ -5196,7 +6104,9 @@
       <c r="G90" s="2"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A91" s="6"/>
+      <c r="A91" s="6" t="s">
+        <v>345</v>
+      </c>
       <c r="B91" s="3" t="b">
         <v>0</v>
       </c>
@@ -5215,7 +6125,9 @@
       <c r="G91" s="2"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A92" s="6"/>
+      <c r="A92" s="6" t="s">
+        <v>346</v>
+      </c>
       <c r="B92" s="3" t="b">
         <v>0</v>
       </c>
@@ -5234,7 +6146,9 @@
       <c r="G92" s="2"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A93" s="6"/>
+      <c r="A93" s="6" t="s">
+        <v>347</v>
+      </c>
       <c r="B93" s="3" t="b">
         <v>0</v>
       </c>
@@ -5253,7 +6167,9 @@
       <c r="G93" s="2"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A94" s="6"/>
+      <c r="A94" s="6" t="s">
+        <v>348</v>
+      </c>
       <c r="B94" s="3" t="b">
         <v>0</v>
       </c>
@@ -5272,7 +6188,9 @@
       <c r="G94" s="2"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A95" s="6"/>
+      <c r="A95" s="6" t="s">
+        <v>349</v>
+      </c>
       <c r="B95" s="3" t="b">
         <v>0</v>
       </c>
@@ -5291,7 +6209,9 @@
       <c r="G95" s="2"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A96" s="6"/>
+      <c r="A96" s="6" t="s">
+        <v>350</v>
+      </c>
       <c r="B96" s="3" t="b">
         <v>0</v>
       </c>
@@ -5310,7 +6230,9 @@
       <c r="G96" s="2"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A97" s="6"/>
+      <c r="A97" s="6" t="s">
+        <v>351</v>
+      </c>
       <c r="B97" s="3" t="b">
         <v>0</v>
       </c>
@@ -5329,7 +6251,9 @@
       <c r="G97" s="2"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A98" s="6"/>
+      <c r="A98" s="6" t="s">
+        <v>353</v>
+      </c>
       <c r="B98" s="3" t="b">
         <v>0</v>
       </c>
@@ -5348,7 +6272,9 @@
       <c r="G98" s="2"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A99" s="6"/>
+      <c r="A99" s="6" t="s">
+        <v>352</v>
+      </c>
       <c r="B99" s="3" t="b">
         <v>0</v>
       </c>
@@ -5367,7 +6293,9 @@
       <c r="G99" s="2"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A100" s="6"/>
+      <c r="A100" s="6" t="s">
+        <v>354</v>
+      </c>
       <c r="B100" s="3" t="b">
         <v>0</v>
       </c>
@@ -5386,7 +6314,9 @@
       <c r="G100" s="2"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A101" s="6"/>
+      <c r="A101" s="6" t="s">
+        <v>355</v>
+      </c>
       <c r="B101" s="3" t="b">
         <v>0</v>
       </c>
@@ -5405,7 +6335,9 @@
       <c r="G101" s="2"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A102" s="6"/>
+      <c r="A102" s="6" t="s">
+        <v>356</v>
+      </c>
       <c r="B102" s="3" t="b">
         <v>0</v>
       </c>
@@ -5424,7 +6356,9 @@
       <c r="G102" s="2"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A103" s="6"/>
+      <c r="A103" s="6" t="s">
+        <v>357</v>
+      </c>
       <c r="B103" s="3" t="b">
         <v>0</v>
       </c>
@@ -5443,7 +6377,9 @@
       <c r="G103" s="2"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A104" s="6"/>
+      <c r="A104" s="6" t="s">
+        <v>358</v>
+      </c>
       <c r="B104" s="3" t="b">
         <v>0</v>
       </c>
@@ -5462,7 +6398,9 @@
       <c r="G104" s="2"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A105" s="6"/>
+      <c r="A105" s="6" t="s">
+        <v>359</v>
+      </c>
       <c r="B105" s="3" t="b">
         <v>0</v>
       </c>
@@ -5481,7 +6419,9 @@
       <c r="G105" s="2"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A106" s="6"/>
+      <c r="A106" s="6" t="s">
+        <v>255</v>
+      </c>
       <c r="B106" s="3" t="b">
         <v>0</v>
       </c>
@@ -5500,7 +6440,9 @@
       <c r="G106" s="2"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A107" s="6"/>
+      <c r="A107" s="6" t="s">
+        <v>360</v>
+      </c>
       <c r="B107" s="3" t="b">
         <v>0</v>
       </c>
@@ -5519,7 +6461,9 @@
       <c r="G107" s="2"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A108" s="6"/>
+      <c r="A108" s="6" t="s">
+        <v>361</v>
+      </c>
       <c r="B108" s="3" t="b">
         <v>0</v>
       </c>
@@ -5538,7 +6482,9 @@
       <c r="G108" s="2"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A109" s="6"/>
+      <c r="A109" s="6" t="s">
+        <v>362</v>
+      </c>
       <c r="B109" s="3" t="b">
         <v>0</v>
       </c>
@@ -5557,7 +6503,9 @@
       <c r="G109" s="2"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A110" s="6"/>
+      <c r="A110" s="6" t="s">
+        <v>363</v>
+      </c>
       <c r="B110" s="3" t="b">
         <v>0</v>
       </c>
@@ -5576,7 +6524,9 @@
       <c r="G110" s="2"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A111" s="6"/>
+      <c r="A111" s="6" t="s">
+        <v>364</v>
+      </c>
       <c r="B111" s="3" t="b">
         <v>0</v>
       </c>
@@ -5595,7 +6545,9 @@
       <c r="G111" s="2"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A112" s="6"/>
+      <c r="A112" s="6" t="s">
+        <v>365</v>
+      </c>
       <c r="B112" s="3" t="b">
         <v>0</v>
       </c>
@@ -5614,7 +6566,9 @@
       <c r="G112" s="2"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A113" s="6"/>
+      <c r="A113" s="6" t="s">
+        <v>366</v>
+      </c>
       <c r="B113" s="3" t="b">
         <v>0</v>
       </c>
@@ -5633,7 +6587,9 @@
       <c r="G113" s="2"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A114" s="6"/>
+      <c r="A114" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="B114" s="3" t="b">
         <v>0</v>
       </c>
@@ -5652,7 +6608,9 @@
       <c r="G114" s="2"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A115" s="6"/>
+      <c r="A115" s="6" t="s">
+        <v>368</v>
+      </c>
       <c r="B115" s="3" t="b">
         <v>0</v>
       </c>
@@ -5671,7 +6629,9 @@
       <c r="G115" s="2"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A116" s="6"/>
+      <c r="A116" s="6" t="s">
+        <v>369</v>
+      </c>
       <c r="B116" s="3" t="b">
         <v>0</v>
       </c>
@@ -5690,7 +6650,9 @@
       <c r="G116" s="2"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A117" s="6"/>
+      <c r="A117" s="6" t="s">
+        <v>370</v>
+      </c>
       <c r="B117" s="3" t="b">
         <v>0</v>
       </c>
@@ -5709,7 +6671,9 @@
       <c r="G117" s="2"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A118" s="6"/>
+      <c r="A118" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="B118" s="3" t="b">
         <v>0</v>
       </c>
@@ -5728,7 +6692,9 @@
       <c r="G118" s="2"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A119" s="6"/>
+      <c r="A119" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="B119" s="3" t="b">
         <v>0</v>
       </c>
@@ -5747,7 +6713,9 @@
       <c r="G119" s="2"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A120" s="6"/>
+      <c r="A120" s="6" t="s">
+        <v>373</v>
+      </c>
       <c r="B120" s="3" t="b">
         <v>0</v>
       </c>
@@ -5766,7 +6734,9 @@
       <c r="G120" s="2"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A121" s="6"/>
+      <c r="A121" s="6" t="s">
+        <v>374</v>
+      </c>
       <c r="B121" s="3" t="b">
         <v>0</v>
       </c>
@@ -5785,7 +6755,9 @@
       <c r="G121" s="2"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A122" s="6"/>
+      <c r="A122" s="6" t="s">
+        <v>375</v>
+      </c>
       <c r="B122" s="3" t="b">
         <v>0</v>
       </c>
@@ -5804,7 +6776,9 @@
       <c r="G122" s="2"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A123" s="6"/>
+      <c r="A123" s="6" t="s">
+        <v>376</v>
+      </c>
       <c r="B123" s="3" t="b">
         <v>0</v>
       </c>
@@ -5821,6 +6795,132 @@
         <v>0</v>
       </c>
       <c r="G123" s="2"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A124" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B124" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G124" s="2"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A125" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="B125" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G125" s="2"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A126" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="B126" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G126" s="2"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A127" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="B127" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C127" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D127" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E127" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F127" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G127" s="2"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A128" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B128" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G128" s="2"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A129" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B129" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C129" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D129" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E129" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F129" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G129" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5832,7 +6932,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.6328125" bestFit="1" customWidth="1"/>
@@ -5867,7 +6967,9 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6" t="s">
+        <v>133</v>
+      </c>
       <c r="B2" s="3" t="b">
         <v>0</v>
       </c>
@@ -5886,7 +6988,9 @@
       <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="6"/>
+      <c r="A3" s="6" t="s">
+        <v>134</v>
+      </c>
       <c r="B3" s="3" t="b">
         <v>0</v>
       </c>
@@ -5905,7 +7009,9 @@
       <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="6"/>
+      <c r="A4" s="6" t="s">
+        <v>135</v>
+      </c>
       <c r="B4" s="3" t="b">
         <v>0</v>
       </c>
@@ -5924,7 +7030,9 @@
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
+      <c r="A5" s="6" t="s">
+        <v>136</v>
+      </c>
       <c r="B5" s="3" t="b">
         <v>0</v>
       </c>
@@ -5943,7 +7051,9 @@
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="6"/>
+      <c r="A6" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="B6" s="3" t="b">
         <v>0</v>
       </c>
@@ -5962,7 +7072,9 @@
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="6"/>
+      <c r="A7" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="B7" s="3" t="b">
         <v>0</v>
       </c>
@@ -5981,7 +7093,9 @@
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="6"/>
+      <c r="A8" s="6" t="s">
+        <v>139</v>
+      </c>
       <c r="B8" s="3" t="b">
         <v>0</v>
       </c>
@@ -6000,7 +7114,9 @@
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="6"/>
+      <c r="A9" s="6" t="s">
+        <v>140</v>
+      </c>
       <c r="B9" s="3" t="b">
         <v>0</v>
       </c>
@@ -6019,7 +7135,9 @@
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="6"/>
+      <c r="A10" s="6" t="s">
+        <v>141</v>
+      </c>
       <c r="B10" s="3" t="b">
         <v>0</v>
       </c>
@@ -6038,7 +7156,9 @@
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="6"/>
+      <c r="A11" s="6" t="s">
+        <v>142</v>
+      </c>
       <c r="B11" s="3" t="b">
         <v>0</v>
       </c>
@@ -6057,7 +7177,9 @@
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="6"/>
+      <c r="A12" s="6" t="s">
+        <v>144</v>
+      </c>
       <c r="B12" s="3" t="b">
         <v>0</v>
       </c>
@@ -6076,7 +7198,9 @@
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="6"/>
+      <c r="A13" s="6" t="s">
+        <v>143</v>
+      </c>
       <c r="B13" s="3" t="b">
         <v>0</v>
       </c>
@@ -6095,7 +7219,9 @@
       <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="6"/>
+      <c r="A14" s="6" t="s">
+        <v>145</v>
+      </c>
       <c r="B14" s="3" t="b">
         <v>0</v>
       </c>
@@ -6114,7 +7240,9 @@
       <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="6"/>
+      <c r="A15" s="6" t="s">
+        <v>146</v>
+      </c>
       <c r="B15" s="3" t="b">
         <v>0</v>
       </c>
@@ -6133,7 +7261,9 @@
       <c r="G15" s="4"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="6"/>
+      <c r="A16" s="6" t="s">
+        <v>147</v>
+      </c>
       <c r="B16" s="3" t="b">
         <v>0</v>
       </c>
@@ -6152,7 +7282,9 @@
       <c r="G16" s="4"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="6"/>
+      <c r="A17" s="6" t="s">
+        <v>147</v>
+      </c>
       <c r="B17" s="3" t="b">
         <v>0</v>
       </c>
@@ -6171,7 +7303,9 @@
       <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="6"/>
+      <c r="A18" s="6" t="s">
+        <v>148</v>
+      </c>
       <c r="B18" s="3" t="b">
         <v>0</v>
       </c>
@@ -6190,7 +7324,9 @@
       <c r="G18" s="4"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="6"/>
+      <c r="A19" s="6" t="s">
+        <v>149</v>
+      </c>
       <c r="B19" s="3" t="b">
         <v>0</v>
       </c>
@@ -6209,7 +7345,9 @@
       <c r="G19" s="4"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="6"/>
+      <c r="A20" s="6" t="s">
+        <v>150</v>
+      </c>
       <c r="B20" s="3" t="b">
         <v>0</v>
       </c>
@@ -6228,7 +7366,9 @@
       <c r="G20" s="4"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="6"/>
+      <c r="A21" s="6" t="s">
+        <v>151</v>
+      </c>
       <c r="B21" s="3" t="b">
         <v>0</v>
       </c>
@@ -6247,7 +7387,9 @@
       <c r="G21" s="4"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="6"/>
+      <c r="A22" s="6" t="s">
+        <v>152</v>
+      </c>
       <c r="B22" s="3" t="b">
         <v>0</v>
       </c>
@@ -6266,7 +7408,9 @@
       <c r="G22" s="4"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="6"/>
+      <c r="A23" s="6" t="s">
+        <v>153</v>
+      </c>
       <c r="B23" s="3" t="b">
         <v>0</v>
       </c>
@@ -6285,7 +7429,9 @@
       <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="6"/>
+      <c r="A24" s="6" t="s">
+        <v>154</v>
+      </c>
       <c r="B24" s="3" t="b">
         <v>0</v>
       </c>
@@ -6304,7 +7450,9 @@
       <c r="G24" s="4"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="6"/>
+      <c r="A25" s="6" t="s">
+        <v>155</v>
+      </c>
       <c r="B25" s="3" t="b">
         <v>0</v>
       </c>
@@ -6323,7 +7471,9 @@
       <c r="G25" s="4"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="6"/>
+      <c r="A26" s="6" t="s">
+        <v>156</v>
+      </c>
       <c r="B26" s="3" t="b">
         <v>0</v>
       </c>
@@ -6342,7 +7492,9 @@
       <c r="G26" s="4"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="6"/>
+      <c r="A27" s="6" t="s">
+        <v>157</v>
+      </c>
       <c r="B27" s="3" t="b">
         <v>0</v>
       </c>
@@ -6361,7 +7513,9 @@
       <c r="G27" s="4"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" s="6"/>
+      <c r="A28" s="6" t="s">
+        <v>158</v>
+      </c>
       <c r="B28" s="3" t="b">
         <v>0</v>
       </c>
@@ -6380,7 +7534,9 @@
       <c r="G28" s="4"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="6"/>
+      <c r="A29" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="B29" s="3" t="b">
         <v>0</v>
       </c>
@@ -6399,7 +7555,9 @@
       <c r="G29" s="4"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="6"/>
+      <c r="A30" s="6" t="s">
+        <v>160</v>
+      </c>
       <c r="B30" s="3" t="b">
         <v>0</v>
       </c>
@@ -6418,7 +7576,9 @@
       <c r="G30" s="4"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="6"/>
+      <c r="A31" s="6" t="s">
+        <v>161</v>
+      </c>
       <c r="B31" s="3" t="b">
         <v>0</v>
       </c>
@@ -6437,7 +7597,9 @@
       <c r="G31" s="4"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="6"/>
+      <c r="A32" s="6" t="s">
+        <v>162</v>
+      </c>
       <c r="B32" s="3" t="b">
         <v>0</v>
       </c>
@@ -6456,7 +7618,9 @@
       <c r="G32" s="4"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="6"/>
+      <c r="A33" s="6" t="s">
+        <v>163</v>
+      </c>
       <c r="B33" s="3" t="b">
         <v>0</v>
       </c>
@@ -6475,7 +7639,9 @@
       <c r="G33" s="4"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="6"/>
+      <c r="A34" s="6" t="s">
+        <v>164</v>
+      </c>
       <c r="B34" s="3" t="b">
         <v>0</v>
       </c>
@@ -6494,7 +7660,9 @@
       <c r="G34" s="4"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="6"/>
+      <c r="A35" s="6" t="s">
+        <v>165</v>
+      </c>
       <c r="B35" s="3" t="b">
         <v>0</v>
       </c>
@@ -6513,7 +7681,9 @@
       <c r="G35" s="4"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="6"/>
+      <c r="A36" s="6" t="s">
+        <v>166</v>
+      </c>
       <c r="B36" s="3" t="b">
         <v>0</v>
       </c>
@@ -6532,7 +7702,9 @@
       <c r="G36" s="4"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="6"/>
+      <c r="A37" s="6" t="s">
+        <v>167</v>
+      </c>
       <c r="B37" s="3" t="b">
         <v>0</v>
       </c>
@@ -6551,7 +7723,9 @@
       <c r="G37" s="4"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="6"/>
+      <c r="A38" s="6" t="s">
+        <v>168</v>
+      </c>
       <c r="B38" s="3" t="b">
         <v>0</v>
       </c>
@@ -6570,7 +7744,9 @@
       <c r="G38" s="4"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" s="6"/>
+      <c r="A39" s="6" t="s">
+        <v>169</v>
+      </c>
       <c r="B39" s="3" t="b">
         <v>0</v>
       </c>
@@ -6589,7 +7765,9 @@
       <c r="G39" s="4"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="6"/>
+      <c r="A40" s="6" t="s">
+        <v>170</v>
+      </c>
       <c r="B40" s="3" t="b">
         <v>0</v>
       </c>
@@ -6608,7 +7786,9 @@
       <c r="G40" s="4"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="6"/>
+      <c r="A41" s="6" t="s">
+        <v>171</v>
+      </c>
       <c r="B41" s="3" t="b">
         <v>0</v>
       </c>
@@ -6627,7 +7807,9 @@
       <c r="G41" s="4"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" s="6"/>
+      <c r="A42" s="6" t="s">
+        <v>172</v>
+      </c>
       <c r="B42" s="3" t="b">
         <v>0</v>
       </c>
@@ -6646,7 +7828,9 @@
       <c r="G42" s="4"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="6"/>
+      <c r="A43" s="6" t="s">
+        <v>173</v>
+      </c>
       <c r="B43" s="3" t="b">
         <v>0</v>
       </c>
@@ -6665,7 +7849,9 @@
       <c r="G43" s="4"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="6"/>
+      <c r="A44" s="6" t="s">
+        <v>174</v>
+      </c>
       <c r="B44" s="3" t="b">
         <v>0</v>
       </c>
@@ -6684,7 +7870,9 @@
       <c r="G44" s="4"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="6"/>
+      <c r="A45" s="6" t="s">
+        <v>175</v>
+      </c>
       <c r="B45" s="3" t="b">
         <v>0</v>
       </c>
@@ -6703,7 +7891,9 @@
       <c r="G45" s="4"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" s="6"/>
+      <c r="A46" s="6" t="s">
+        <v>176</v>
+      </c>
       <c r="B46" s="3" t="b">
         <v>0</v>
       </c>
@@ -6722,7 +7912,9 @@
       <c r="G46" s="4"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="6"/>
+      <c r="A47" s="6" t="s">
+        <v>177</v>
+      </c>
       <c r="B47" s="3" t="b">
         <v>0</v>
       </c>
@@ -6741,7 +7933,9 @@
       <c r="G47" s="4"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" s="6"/>
+      <c r="A48" s="6" t="s">
+        <v>178</v>
+      </c>
       <c r="B48" s="3" t="b">
         <v>0</v>
       </c>
@@ -6760,7 +7954,9 @@
       <c r="G48" s="4"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A49" s="6"/>
+      <c r="A49" s="6" t="s">
+        <v>179</v>
+      </c>
       <c r="B49" s="3" t="b">
         <v>0</v>
       </c>
@@ -6779,7 +7975,9 @@
       <c r="G49" s="4"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A50" s="6"/>
+      <c r="A50" s="6" t="s">
+        <v>180</v>
+      </c>
       <c r="B50" s="3" t="b">
         <v>0</v>
       </c>
@@ -6798,7 +7996,9 @@
       <c r="G50" s="4"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A51" s="6"/>
+      <c r="A51" s="6" t="s">
+        <v>181</v>
+      </c>
       <c r="B51" s="3" t="b">
         <v>0</v>
       </c>
@@ -6817,7 +8017,9 @@
       <c r="G51" s="4"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52" s="6"/>
+      <c r="A52" s="6" t="s">
+        <v>182</v>
+      </c>
       <c r="B52" s="3" t="b">
         <v>0</v>
       </c>
@@ -6836,7 +8038,9 @@
       <c r="G52" s="4"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53" s="6"/>
+      <c r="A53" s="6" t="s">
+        <v>183</v>
+      </c>
       <c r="B53" s="3" t="b">
         <v>0</v>
       </c>
@@ -6855,7 +8059,9 @@
       <c r="G53" s="4"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" s="6"/>
+      <c r="A54" s="6" t="s">
+        <v>184</v>
+      </c>
       <c r="B54" s="3" t="b">
         <v>0</v>
       </c>
@@ -6874,7 +8080,9 @@
       <c r="G54" s="4"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A55" s="6"/>
+      <c r="A55" s="6" t="s">
+        <v>185</v>
+      </c>
       <c r="B55" s="3" t="b">
         <v>0</v>
       </c>
@@ -6893,7 +8101,9 @@
       <c r="G55" s="4"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56" s="6"/>
+      <c r="A56" s="6" t="s">
+        <v>186</v>
+      </c>
       <c r="B56" s="3" t="b">
         <v>0</v>
       </c>
@@ -6912,7 +8122,9 @@
       <c r="G56" s="4"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A57" s="6"/>
+      <c r="A57" s="6" t="s">
+        <v>187</v>
+      </c>
       <c r="B57" s="3" t="b">
         <v>0</v>
       </c>
@@ -6931,7 +8143,9 @@
       <c r="G57" s="4"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A58" s="6"/>
+      <c r="A58" s="6" t="s">
+        <v>188</v>
+      </c>
       <c r="B58" s="3" t="b">
         <v>0</v>
       </c>
@@ -6950,7 +8164,9 @@
       <c r="G58" s="4"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A59" s="6"/>
+      <c r="A59" s="6" t="s">
+        <v>189</v>
+      </c>
       <c r="B59" s="3" t="b">
         <v>0</v>
       </c>
@@ -6969,7 +8185,9 @@
       <c r="G59" s="4"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A60" s="6"/>
+      <c r="A60" s="6" t="s">
+        <v>190</v>
+      </c>
       <c r="B60" s="3" t="b">
         <v>0</v>
       </c>
@@ -6988,7 +8206,9 @@
       <c r="G60" s="4"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A61" s="6"/>
+      <c r="A61" s="6" t="s">
+        <v>191</v>
+      </c>
       <c r="B61" s="3" t="b">
         <v>0</v>
       </c>
@@ -7007,7 +8227,9 @@
       <c r="G61" s="4"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A62" s="6"/>
+      <c r="A62" s="6" t="s">
+        <v>192</v>
+      </c>
       <c r="B62" s="3" t="b">
         <v>0</v>
       </c>
@@ -7026,7 +8248,9 @@
       <c r="G62" s="4"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A63" s="6"/>
+      <c r="A63" s="6" t="s">
+        <v>193</v>
+      </c>
       <c r="B63" s="3" t="b">
         <v>0</v>
       </c>
@@ -7045,7 +8269,9 @@
       <c r="G63" s="4"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A64" s="6"/>
+      <c r="A64" s="6" t="s">
+        <v>194</v>
+      </c>
       <c r="B64" s="3" t="b">
         <v>0</v>
       </c>
@@ -7064,7 +8290,9 @@
       <c r="G64" s="4"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A65" s="6"/>
+      <c r="A65" s="6" t="s">
+        <v>195</v>
+      </c>
       <c r="B65" s="3" t="b">
         <v>0</v>
       </c>
@@ -7083,7 +8311,9 @@
       <c r="G65" s="4"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A66" s="6"/>
+      <c r="A66" s="6" t="s">
+        <v>196</v>
+      </c>
       <c r="B66" s="3" t="b">
         <v>0</v>
       </c>
@@ -7102,7 +8332,9 @@
       <c r="G66" s="4"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A67" s="6"/>
+      <c r="A67" s="6" t="s">
+        <v>197</v>
+      </c>
       <c r="B67" s="3" t="b">
         <v>0</v>
       </c>
@@ -7121,7 +8353,9 @@
       <c r="G67" s="4"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A68" s="6"/>
+      <c r="A68" s="6" t="s">
+        <v>198</v>
+      </c>
       <c r="B68" s="3" t="b">
         <v>0</v>
       </c>
@@ -7140,7 +8374,9 @@
       <c r="G68" s="4"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A69" s="6"/>
+      <c r="A69" s="6" t="s">
+        <v>199</v>
+      </c>
       <c r="B69" s="3" t="b">
         <v>0</v>
       </c>
@@ -7159,7 +8395,9 @@
       <c r="G69" s="4"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A70" s="6"/>
+      <c r="A70" s="6" t="s">
+        <v>200</v>
+      </c>
       <c r="B70" s="3" t="b">
         <v>0</v>
       </c>
@@ -7178,7 +8416,9 @@
       <c r="G70" s="4"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A71" s="6"/>
+      <c r="A71" s="6" t="s">
+        <v>201</v>
+      </c>
       <c r="B71" s="3" t="b">
         <v>0</v>
       </c>
@@ -7197,7 +8437,9 @@
       <c r="G71" s="4"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A72" s="6"/>
+      <c r="A72" s="6" t="s">
+        <v>202</v>
+      </c>
       <c r="B72" s="3" t="b">
         <v>0</v>
       </c>
@@ -7216,7 +8458,9 @@
       <c r="G72" s="4"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A73" s="6"/>
+      <c r="A73" s="6" t="s">
+        <v>203</v>
+      </c>
       <c r="B73" s="3" t="b">
         <v>0</v>
       </c>
@@ -7235,7 +8479,9 @@
       <c r="G73" s="4"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A74" s="6"/>
+      <c r="A74" s="6" t="s">
+        <v>204</v>
+      </c>
       <c r="B74" s="3" t="b">
         <v>0</v>
       </c>
@@ -7254,7 +8500,9 @@
       <c r="G74" s="4"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A75" s="6"/>
+      <c r="A75" s="6" t="s">
+        <v>205</v>
+      </c>
       <c r="B75" s="3" t="b">
         <v>0</v>
       </c>
@@ -7273,7 +8521,9 @@
       <c r="G75" s="4"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A76" s="6"/>
+      <c r="A76" s="6" t="s">
+        <v>206</v>
+      </c>
       <c r="B76" s="3" t="b">
         <v>0</v>
       </c>
@@ -7292,7 +8542,9 @@
       <c r="G76" s="4"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A77" s="6"/>
+      <c r="A77" s="6" t="s">
+        <v>207</v>
+      </c>
       <c r="B77" s="3" t="b">
         <v>0</v>
       </c>
@@ -7311,7 +8563,9 @@
       <c r="G77" s="4"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A78" s="6"/>
+      <c r="A78" s="6" t="s">
+        <v>208</v>
+      </c>
       <c r="B78" s="3" t="b">
         <v>0</v>
       </c>
@@ -7330,7 +8584,9 @@
       <c r="G78" s="4"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A79" s="6"/>
+      <c r="A79" s="6" t="s">
+        <v>209</v>
+      </c>
       <c r="B79" s="3" t="b">
         <v>0</v>
       </c>
@@ -7349,7 +8605,9 @@
       <c r="G79" s="4"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A80" s="6"/>
+      <c r="A80" s="6" t="s">
+        <v>210</v>
+      </c>
       <c r="B80" s="3" t="b">
         <v>0</v>
       </c>
@@ -7368,7 +8626,9 @@
       <c r="G80" s="4"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A81" s="6"/>
+      <c r="A81" s="6" t="s">
+        <v>211</v>
+      </c>
       <c r="B81" s="3" t="b">
         <v>0</v>
       </c>
@@ -7387,7 +8647,9 @@
       <c r="G81" s="4"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A82" s="6"/>
+      <c r="A82" s="6" t="s">
+        <v>212</v>
+      </c>
       <c r="B82" s="3" t="b">
         <v>0</v>
       </c>
@@ -7406,7 +8668,9 @@
       <c r="G82" s="4"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A83" s="6"/>
+      <c r="A83" s="6" t="s">
+        <v>213</v>
+      </c>
       <c r="B83" s="3" t="b">
         <v>0</v>
       </c>
@@ -7425,7 +8689,9 @@
       <c r="G83" s="4"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A84" s="6"/>
+      <c r="A84" s="6" t="s">
+        <v>214</v>
+      </c>
       <c r="B84" s="3" t="b">
         <v>0</v>
       </c>
@@ -7444,7 +8710,9 @@
       <c r="G84" s="4"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A85" s="6"/>
+      <c r="A85" s="6" t="s">
+        <v>215</v>
+      </c>
       <c r="B85" s="3" t="b">
         <v>0</v>
       </c>
@@ -7463,7 +8731,9 @@
       <c r="G85" s="4"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A86" s="6"/>
+      <c r="A86" s="6" t="s">
+        <v>216</v>
+      </c>
       <c r="B86" s="3" t="b">
         <v>0</v>
       </c>
@@ -7482,7 +8752,9 @@
       <c r="G86" s="4"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A87" s="6"/>
+      <c r="A87" s="6" t="s">
+        <v>217</v>
+      </c>
       <c r="B87" s="3" t="b">
         <v>0</v>
       </c>
@@ -7501,7 +8773,9 @@
       <c r="G87" s="4"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A88" s="6"/>
+      <c r="A88" s="6" t="s">
+        <v>218</v>
+      </c>
       <c r="B88" s="3" t="b">
         <v>0</v>
       </c>
@@ -7520,7 +8794,9 @@
       <c r="G88" s="4"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A89" s="6"/>
+      <c r="A89" s="6" t="s">
+        <v>219</v>
+      </c>
       <c r="B89" s="3" t="b">
         <v>0</v>
       </c>
@@ -7539,7 +8815,9 @@
       <c r="G89" s="4"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A90" s="6"/>
+      <c r="A90" s="6" t="s">
+        <v>220</v>
+      </c>
       <c r="B90" s="3" t="b">
         <v>0</v>
       </c>
@@ -7558,7 +8836,9 @@
       <c r="G90" s="4"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A91" s="6"/>
+      <c r="A91" s="6" t="s">
+        <v>221</v>
+      </c>
       <c r="B91" s="3" t="b">
         <v>0</v>
       </c>
@@ -7577,7 +8857,9 @@
       <c r="G91" s="4"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A92" s="6"/>
+      <c r="A92" s="6" t="s">
+        <v>222</v>
+      </c>
       <c r="B92" s="3" t="b">
         <v>0</v>
       </c>
@@ -7596,7 +8878,9 @@
       <c r="G92" s="4"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A93" s="6"/>
+      <c r="A93" s="6" t="s">
+        <v>223</v>
+      </c>
       <c r="B93" s="3" t="b">
         <v>0</v>
       </c>
@@ -7615,7 +8899,9 @@
       <c r="G93" s="4"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A94" s="6"/>
+      <c r="A94" s="6" t="s">
+        <v>224</v>
+      </c>
       <c r="B94" s="3" t="b">
         <v>0</v>
       </c>
@@ -7634,7 +8920,9 @@
       <c r="G94" s="4"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A95" s="6"/>
+      <c r="A95" s="6" t="s">
+        <v>225</v>
+      </c>
       <c r="B95" s="3" t="b">
         <v>0</v>
       </c>
@@ -7653,7 +8941,9 @@
       <c r="G95" s="4"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A96" s="6"/>
+      <c r="A96" s="6" t="s">
+        <v>226</v>
+      </c>
       <c r="B96" s="3" t="b">
         <v>0</v>
       </c>
@@ -7672,7 +8962,9 @@
       <c r="G96" s="4"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A97" s="6"/>
+      <c r="A97" s="6" t="s">
+        <v>227</v>
+      </c>
       <c r="B97" s="3" t="b">
         <v>0</v>
       </c>
@@ -7691,7 +8983,9 @@
       <c r="G97" s="4"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A98" s="6"/>
+      <c r="A98" s="6" t="s">
+        <v>228</v>
+      </c>
       <c r="B98" s="3" t="b">
         <v>0</v>
       </c>
@@ -7710,7 +9004,9 @@
       <c r="G98" s="4"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A99" s="6"/>
+      <c r="A99" s="6" t="s">
+        <v>229</v>
+      </c>
       <c r="B99" s="3" t="b">
         <v>0</v>
       </c>
@@ -7729,7 +9025,9 @@
       <c r="G99" s="4"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A100" s="6"/>
+      <c r="A100" s="6" t="s">
+        <v>230</v>
+      </c>
       <c r="B100" s="3" t="b">
         <v>0</v>
       </c>
@@ -7748,7 +9046,9 @@
       <c r="G100" s="4"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A101" s="6"/>
+      <c r="A101" s="6" t="s">
+        <v>231</v>
+      </c>
       <c r="B101" s="3" t="b">
         <v>0</v>
       </c>
@@ -7767,7 +9067,9 @@
       <c r="G101" s="4"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A102" s="6"/>
+      <c r="A102" s="6" t="s">
+        <v>232</v>
+      </c>
       <c r="B102" s="3" t="b">
         <v>0</v>
       </c>
@@ -7786,7 +9088,9 @@
       <c r="G102" s="4"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A103" s="6"/>
+      <c r="A103" s="6" t="s">
+        <v>233</v>
+      </c>
       <c r="B103" s="3" t="b">
         <v>0</v>
       </c>
@@ -7805,7 +9109,9 @@
       <c r="G103" s="4"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A104" s="6"/>
+      <c r="A104" s="6" t="s">
+        <v>234</v>
+      </c>
       <c r="B104" s="3" t="b">
         <v>0</v>
       </c>
@@ -7824,7 +9130,9 @@
       <c r="G104" s="4"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A105" s="6"/>
+      <c r="A105" s="6" t="s">
+        <v>235</v>
+      </c>
       <c r="B105" s="3" t="b">
         <v>0</v>
       </c>
@@ -7843,7 +9151,9 @@
       <c r="G105" s="4"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A106" s="6"/>
+      <c r="A106" s="6" t="s">
+        <v>236</v>
+      </c>
       <c r="B106" s="3" t="b">
         <v>0</v>
       </c>
@@ -7862,7 +9172,9 @@
       <c r="G106" s="4"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A107" s="6"/>
+      <c r="A107" s="6" t="s">
+        <v>237</v>
+      </c>
       <c r="B107" s="3" t="b">
         <v>0</v>
       </c>
@@ -7881,7 +9193,9 @@
       <c r="G107" s="4"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A108" s="6"/>
+      <c r="A108" s="6" t="s">
+        <v>237</v>
+      </c>
       <c r="B108" s="3" t="b">
         <v>0</v>
       </c>
@@ -7900,7 +9214,9 @@
       <c r="G108" s="4"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A109" s="6"/>
+      <c r="A109" s="6" t="s">
+        <v>238</v>
+      </c>
       <c r="B109" s="3" t="b">
         <v>0</v>
       </c>
@@ -7919,7 +9235,9 @@
       <c r="G109" s="4"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A110" s="6"/>
+      <c r="A110" s="6" t="s">
+        <v>239</v>
+      </c>
       <c r="B110" s="3" t="b">
         <v>0</v>
       </c>
@@ -7938,7 +9256,9 @@
       <c r="G110" s="4"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A111" s="6"/>
+      <c r="A111" s="6" t="s">
+        <v>240</v>
+      </c>
       <c r="B111" s="3" t="b">
         <v>0</v>
       </c>
@@ -7957,7 +9277,9 @@
       <c r="G111" s="4"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A112" s="6"/>
+      <c r="A112" s="6" t="s">
+        <v>241</v>
+      </c>
       <c r="B112" s="3" t="b">
         <v>0</v>
       </c>
@@ -7976,7 +9298,9 @@
       <c r="G112" s="4"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A113" s="6"/>
+      <c r="A113" s="6" t="s">
+        <v>242</v>
+      </c>
       <c r="B113" s="3" t="b">
         <v>0</v>
       </c>
@@ -7995,7 +9319,9 @@
       <c r="G113" s="4"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A114" s="6"/>
+      <c r="A114" s="6" t="s">
+        <v>243</v>
+      </c>
       <c r="B114" s="3" t="b">
         <v>0</v>
       </c>
@@ -8014,7 +9340,9 @@
       <c r="G114" s="4"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A115" s="6"/>
+      <c r="A115" s="6" t="s">
+        <v>244</v>
+      </c>
       <c r="B115" s="3" t="b">
         <v>0</v>
       </c>
@@ -8033,7 +9361,9 @@
       <c r="G115" s="4"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A116" s="6"/>
+      <c r="A116" s="6" t="s">
+        <v>245</v>
+      </c>
       <c r="B116" s="3" t="b">
         <v>0</v>
       </c>
@@ -8052,7 +9382,9 @@
       <c r="G116" s="4"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A117" s="6"/>
+      <c r="A117" s="6" t="s">
+        <v>246</v>
+      </c>
       <c r="B117" s="3" t="b">
         <v>0</v>
       </c>
@@ -8071,7 +9403,9 @@
       <c r="G117" s="4"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A118" s="6"/>
+      <c r="A118" s="6" t="s">
+        <v>247</v>
+      </c>
       <c r="B118" s="3" t="b">
         <v>0</v>
       </c>
@@ -8090,7 +9424,9 @@
       <c r="G118" s="4"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A119" s="6"/>
+      <c r="A119" s="6" t="s">
+        <v>248</v>
+      </c>
       <c r="B119" s="3" t="b">
         <v>0</v>
       </c>
@@ -8109,7 +9445,9 @@
       <c r="G119" s="4"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A120" s="6"/>
+      <c r="A120" s="6" t="s">
+        <v>249</v>
+      </c>
       <c r="B120" s="3" t="b">
         <v>0</v>
       </c>
@@ -8128,7 +9466,9 @@
       <c r="G120" s="4"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A121" s="6"/>
+      <c r="A121" s="6" t="s">
+        <v>250</v>
+      </c>
       <c r="B121" s="3" t="b">
         <v>0</v>
       </c>
@@ -8147,7 +9487,9 @@
       <c r="G121" s="4"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A122" s="6"/>
+      <c r="A122" s="6" t="s">
+        <v>251</v>
+      </c>
       <c r="B122" s="3" t="b">
         <v>0</v>
       </c>
@@ -8164,6 +9506,90 @@
         <v>0</v>
       </c>
       <c r="G122" s="4"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A123" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="B123" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G123" s="2"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A124" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="B124" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G124" s="2"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A125" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B125" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G125" s="2"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A126" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="B126" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G126" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
